--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D730"/>
+  <dimension ref="A1:D732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13570,6 +13570,42 @@
       <c r="D730" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>277.07</v>
+      </c>
+      <c r="C731" t="n">
+        <v>226.31</v>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>278.76</v>
+      </c>
+      <c r="C732" t="n">
+        <v>226.84</v>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B975"/>
+  <dimension ref="A1:B977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23337,6 +23373,26 @@
       </c>
       <c r="B975" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -23499,28 +23555,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1670709963621977</v>
+        <v>0.16796721128325</v>
       </c>
       <c r="J2" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="K2" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06622152311485741</v>
+        <v>0.06728028738750835</v>
       </c>
       <c r="M2" t="n">
-        <v>4.115397933740239</v>
+        <v>4.108833872209702</v>
       </c>
       <c r="N2" t="n">
-        <v>23.40445887275477</v>
+        <v>23.34951143040378</v>
       </c>
       <c r="O2" t="n">
-        <v>4.837815506274993</v>
+        <v>4.832133217369299</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7745476939259</v>
+        <v>271.7655367796455</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23571,28 +23627,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.128917165198425</v>
+        <v>0.1285947741527588</v>
       </c>
       <c r="J3" t="n">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="K3" t="n">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1260975622702389</v>
+        <v>0.1262659275007363</v>
       </c>
       <c r="M3" t="n">
-        <v>2.157708730250934</v>
+        <v>2.153291941668205</v>
       </c>
       <c r="N3" t="n">
-        <v>6.822920778539673</v>
+        <v>6.805334967616784</v>
       </c>
       <c r="O3" t="n">
-        <v>2.612072123533283</v>
+        <v>2.608703694867776</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6723154536824</v>
+        <v>223.6755639048368</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23630,7 +23686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D730"/>
+  <dimension ref="A1:D732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39689,6 +39745,50 @@
         </is>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-41.033222404605844,173.02270741996315</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-41.03293377953174,173.02169548354354</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-41.03321311590473,173.022723348881</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-41.03293124932913,173.02170083037015</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D732"/>
+  <dimension ref="A1:D733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13604,6 +13604,24 @@
         <v>226.84</v>
       </c>
       <c r="D732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>280.64</v>
+      </c>
+      <c r="C733" t="n">
+        <v>227.65</v>
+      </c>
+      <c r="D733" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13620,7 +13638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B977"/>
+  <dimension ref="A1:B979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23393,6 +23411,26 @@
       </c>
       <c r="B977" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>
@@ -23555,28 +23593,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.16796721128325</v>
+        <v>0.1691637303728181</v>
       </c>
       <c r="J2" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="K2" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06728028738750835</v>
+        <v>0.06832212644580604</v>
       </c>
       <c r="M2" t="n">
-        <v>4.108833872209702</v>
+        <v>4.109442674484633</v>
       </c>
       <c r="N2" t="n">
-        <v>23.34951143040378</v>
+        <v>23.3429551376382</v>
       </c>
       <c r="O2" t="n">
-        <v>4.832133217369299</v>
+        <v>4.831454764109688</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7655367796455</v>
+        <v>271.7534583201819</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23627,28 +23665,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1285947741527588</v>
+        <v>0.12872897506551</v>
       </c>
       <c r="J3" t="n">
+        <v>732</v>
+      </c>
+      <c r="K3" t="n">
         <v>731</v>
       </c>
-      <c r="K3" t="n">
-        <v>730</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1262659275007363</v>
+        <v>0.1268649984343033</v>
       </c>
       <c r="M3" t="n">
-        <v>2.153291941668205</v>
+        <v>2.151044553250425</v>
       </c>
       <c r="N3" t="n">
-        <v>6.805334967616784</v>
+        <v>6.79634235827496</v>
       </c>
       <c r="O3" t="n">
-        <v>2.608703694867776</v>
+        <v>2.60697954696138</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6755639048368</v>
+        <v>223.6742050370111</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23686,7 +23724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D732"/>
+  <dimension ref="A1:D733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39789,6 +39827,28 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-41.03320278290918,173.02274106861861</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-41.032927382415224,173.0217090019346</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0567/nzd0567.xlsx
+++ b/data/nzd0567/nzd0567.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D733"/>
+  <dimension ref="A1:D735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13622,6 +13622,42 @@
         <v>227.65</v>
       </c>
       <c r="D733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="C734" t="n">
+        <v>227.66</v>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>281.47</v>
+      </c>
+      <c r="C735" t="n">
+        <v>227.58</v>
+      </c>
+      <c r="D735" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13638,7 +13674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B979"/>
+  <dimension ref="A1:B981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23431,6 +23467,26 @@
       </c>
       <c r="B979" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -23593,28 +23649,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1691637303728181</v>
+        <v>0.1720023884154766</v>
       </c>
       <c r="J2" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K2" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06832212644580604</v>
+        <v>0.07071150811834259</v>
       </c>
       <c r="M2" t="n">
-        <v>4.109442674484633</v>
+        <v>4.112917488045395</v>
       </c>
       <c r="N2" t="n">
-        <v>23.3429551376382</v>
+        <v>23.35099263520812</v>
       </c>
       <c r="O2" t="n">
-        <v>4.831454764109688</v>
+        <v>4.832286481077888</v>
       </c>
       <c r="P2" t="n">
-        <v>271.7534583201819</v>
+        <v>271.7247542704642</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23665,28 +23721,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.12872897506551</v>
+        <v>0.1289749588013897</v>
       </c>
       <c r="J3" t="n">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K3" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1268649984343033</v>
+        <v>0.1280307820673127</v>
       </c>
       <c r="M3" t="n">
-        <v>2.151044553250425</v>
+        <v>2.146449546657684</v>
       </c>
       <c r="N3" t="n">
-        <v>6.79634235827496</v>
+        <v>6.778337975876536</v>
       </c>
       <c r="O3" t="n">
-        <v>2.60697954696138</v>
+        <v>2.603524145437591</v>
       </c>
       <c r="P3" t="n">
-        <v>223.6742050370111</v>
+        <v>223.6717100877229</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23724,7 +23780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D733"/>
+  <dimension ref="A1:D735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39849,6 +39905,50 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-41.0331978362614,173.02274955146976</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-41.03292733467554,173.0217091028181</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-41.033198221000696,173.0227488916925</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-41.032927716592994,173.02170829575005</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
